--- a/download/sample_report_restaurant.xlsx
+++ b/download/sample_report_restaurant.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales Breakdown" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales Analysis" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expense Analysis" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommendations" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staff &amp; Operations" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommendations" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,11 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,18 +40,13 @@
     </font>
     <font>
       <name val="Noto Sans CJK SC"/>
-      <color rgb="00B85C1E"/>
-      <sz val="11"/>
+      <color rgb="009C8B78"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Noto Sans CJK SC"/>
       <color rgb="00B85C1E"/>
       <sz val="22"/>
-    </font>
-    <font>
-      <name val="Noto Sans CJK SC"/>
-      <color rgb="009C8B78"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Noto Sans CJK SC"/>
@@ -63,32 +60,11 @@
     </font>
     <font>
       <name val="Noto Sans CJK SC"/>
-      <color rgb="008C8A84"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <color rgb="00C0392B"/>
-    </font>
-    <font>
-      <name val="Noto Sans CJK SC"/>
-      <color rgb="00C0392B"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <color rgb="001B7D46"/>
-    </font>
-    <font>
-      <name val="Noto Sans CJK SC"/>
-      <color rgb="001B7D46"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Noto Sans CJK SC"/>
-      <color rgb="00D4820A"/>
+      <color rgb="00B85C1E"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -115,31 +91,6 @@
         <fgColor rgb="00F5E6D5"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill>
-        <bgColor rgb="00FDEDEC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill>
-        <bgColor rgb="00E8F5E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDEDEC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEF9E7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F5E9"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -163,102 +114,140 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="00C0392B"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FDEDEC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="001B7D46"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00E8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="00D4820A"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FEF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -351,7 +340,7 @@
                 <a:latin typeface="Noto Sans CJK SC"/>
                 <a:ea typeface="Noto Sans CJK SC"/>
               </a:rPr>
-              <a:t>Revenue vs Expenses by Month</a:t>
+              <a:t>Revenue vs Expenses</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -365,9 +354,7 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <strRef>
-              <f>'Dashboard'!C8</f>
-            </strRef>
+            <v>Revenue</v>
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -382,12 +369,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$9:$B$12</f>
+              <f>'Executive Summary'!$B$8:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$C$9:$C$12</f>
+              <f>'Executive Summary'!$C$7:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -395,9 +382,7 @@
           <idx val="1"/>
           <order val="1"/>
           <tx>
-            <strRef>
-              <f>'Dashboard'!D8</f>
-            </strRef>
+            <v>Expenses</v>
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -412,17 +397,17 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$9:$B$12</f>
+              <f>'Executive Summary'!$B$8:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$D$9:$D$12</f>
+              <f>'Executive Summary'!$D$7:$D$13</f>
             </numRef>
           </val>
         </ser>
         <gapWidth val="80"/>
-        <overlap val="-20"/>
+        <overlap val="100"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -432,10 +417,22 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
               <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0">
@@ -448,12 +445,114 @@
                     <a:latin typeface="Noto Sans CJK SC"/>
                     <a:ea typeface="Noto Sans CJK SC"/>
                   </a:rPr>
-                  <a:t>Month</a:t>
+                  <a:t>AED</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="1000" b="0">
+                  <a:latin typeface="Noto Sans CJK SC"/>
+                  <a:ea typeface="Noto Sans CJK SC"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </txPr>
         </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:rPr>
+              <a:t>Peak Hours Revenue</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Avg Revenue</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="B85C1E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="B85C1E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Staff &amp; Operations'!$B$34:$B$39</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Staff &amp; Operations'!$D$33:$D$39</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -549,15 +648,13 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <strRef>
-              <f>'Dashboard'!F8</f>
-            </strRef>
+            <v>Profit Margin</v>
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="B85C1E"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
                 <a:srgbClr val="B85C1E"/>
               </a:solidFill>
@@ -565,8 +662,7 @@
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="circle"/>
-            <size val="7"/>
+            <symbol val="none"/>
             <spPr>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
@@ -575,12 +671,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$9:$B$12</f>
+              <f>'Executive Summary'!$B$8:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$F$9:$F$12</f>
+              <f>'Executive Summary'!$E$7:$E$13</f>
             </numRef>
           </val>
         </ser>
@@ -593,28 +689,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0">
-                    <a:latin typeface="Noto Sans CJK SC"/>
-                    <a:ea typeface="Noto Sans CJK SC"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr sz="1000" b="0">
-                    <a:latin typeface="Noto Sans CJK SC"/>
-                    <a:ea typeface="Noto Sans CJK SC"/>
-                  </a:rPr>
-                  <a:t>Month</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -697,7 +771,143 @@
                 <a:latin typeface="Noto Sans CJK SC"/>
                 <a:ea typeface="Noto Sans CJK SC"/>
               </a:rPr>
-              <a:t>Revenue Share by Category</a:t>
+              <a:t>Monthly Orders Trend</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Orders</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="B85C1E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="B85C1E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Executive Summary'!$B$8:$B$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Executive Summary'!$G$7:$G$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0">
+                    <a:latin typeface="Noto Sans CJK SC"/>
+                    <a:ea typeface="Noto Sans CJK SC"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="1000" b="0">
+                    <a:latin typeface="Noto Sans CJK SC"/>
+                    <a:ea typeface="Noto Sans CJK SC"/>
+                  </a:rPr>
+                  <a:t>Orders</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="1000" b="0">
+                  <a:latin typeface="Noto Sans CJK SC"/>
+                  <a:ea typeface="Noto Sans CJK SC"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </txPr>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:rPr>
+              <a:t>Revenue by Category</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -709,11 +919,6 @@
         <ser>
           <idx val="0"/>
           <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Sales Breakdown'!D4</f>
-            </strRef>
-          </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
@@ -785,14 +990,36 @@
               </a:ln>
             </spPr>
           </dPt>
+          <dPt>
+            <idx val="6"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2E7D32"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="7"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="E65100"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
-              <f>'Sales Breakdown'!$B$5:$B$10</f>
+              <f>'Sales Analysis'!$B$5:$B$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Sales Breakdown'!$D$5:$D$10</f>
+              <f>'Sales Analysis'!$D$4:$D$12</f>
             </numRef>
           </val>
         </ser>
@@ -808,7 +1035,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
@@ -836,15 +1063,13 @@
     </title>
     <plotArea>
       <barChart>
-        <barDir val="bar"/>
+        <barDir val="col"/>
         <grouping val="clustered"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <strRef>
-              <f>'Sales Breakdown'!C4</f>
-            </strRef>
+            <v>Orders</v>
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -859,12 +1084,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Sales Breakdown'!$B$5:$B$10</f>
+              <f>'Sales Analysis'!$B$5:$B$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Sales Breakdown'!$C$5:$C$10</f>
+              <f>'Sales Analysis'!$C$4:$C$12</f>
             </numRef>
           </val>
         </ser>
@@ -879,10 +1104,22 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
               <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0">
@@ -900,19 +1137,21 @@
               </a:p>
             </rich>
           </tx>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="1000" b="0">
+                  <a:latin typeface="Noto Sans CJK SC"/>
+                  <a:ea typeface="Noto Sans CJK SC"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </txPr>
         </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -927,7 +1166,143 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:rPr>
+              <a:t>Daily Revenue — January 2026</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Revenue</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="B85C1E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="B85C1E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Sales Analysis'!$B$34:$B$64</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Sales Analysis'!$C$33:$C$64</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0">
+                    <a:latin typeface="Noto Sans CJK SC"/>
+                    <a:ea typeface="Noto Sans CJK SC"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="1000" b="0">
+                    <a:latin typeface="Noto Sans CJK SC"/>
+                    <a:ea typeface="Noto Sans CJK SC"/>
+                  </a:rPr>
+                  <a:t>AED</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="1000" b="0">
+                  <a:latin typeface="Noto Sans CJK SC"/>
+                  <a:ea typeface="Noto Sans CJK SC"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </txPr>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
@@ -961,9 +1336,7 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <strRef>
-              <f>'Expense Analysis'!C4</f>
-            </strRef>
+            <v>Budget</v>
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -978,12 +1351,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Expense Analysis'!$B$5:$B$12</f>
+              <f>'Expense Analysis'!$B$5:$B$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Expense Analysis'!$C$5:$C$12</f>
+              <f>'Expense Analysis'!$C$4:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -991,9 +1364,7 @@
           <idx val="1"/>
           <order val="1"/>
           <tx>
-            <strRef>
-              <f>'Expense Analysis'!D4</f>
-            </strRef>
+            <v>Actual</v>
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1008,17 +1379,17 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Expense Analysis'!$B$5:$B$12</f>
+              <f>'Expense Analysis'!$B$5:$B$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Expense Analysis'!$D$5:$D$12</f>
+              <f>'Expense Analysis'!$D$4:$D$16</f>
             </numRef>
           </val>
         </ser>
         <gapWidth val="80"/>
-        <overlap val="-20"/>
+        <overlap val="100"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -1028,10 +1399,22 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
               <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0">
@@ -1044,12 +1427,344 @@
                     <a:latin typeface="Noto Sans CJK SC"/>
                     <a:ea typeface="Noto Sans CJK SC"/>
                   </a:rPr>
-                  <a:t>Category</a:t>
+                  <a:t>AED</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="1000" b="0">
+                  <a:latin typeface="Noto Sans CJK SC"/>
+                  <a:ea typeface="Noto Sans CJK SC"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </txPr>
         </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:rPr>
+              <a:t>Monthly Total Expense Trend</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Total Expenses</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="B85C1E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="B85C1E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Expense Analysis'!$B$52:$E$52</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Expense Analysis'!$B$53</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2E7D32"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="2E7D32"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Expense Analysis'!$B$52:$E$52</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Expense Analysis'!$C$53</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="E65100"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E65100"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Expense Analysis'!$B$52:$E$52</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Expense Analysis'!$D$53</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="C62828"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="C62828"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Expense Analysis'!$B$52:$E$52</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Expense Analysis'!$E$53</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0">
+                    <a:latin typeface="Noto Sans CJK SC"/>
+                    <a:ea typeface="Noto Sans CJK SC"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="1000" b="0">
+                    <a:latin typeface="Noto Sans CJK SC"/>
+                    <a:ea typeface="Noto Sans CJK SC"/>
+                  </a:rPr>
+                  <a:t>AED</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="1000" b="0">
+                  <a:latin typeface="Noto Sans CJK SC"/>
+                  <a:ea typeface="Noto Sans CJK SC"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </txPr>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1200" b="0">
+                <a:latin typeface="Noto Sans CJK SC"/>
+                <a:ea typeface="Noto Sans CJK SC"/>
+              </a:rPr>
+              <a:t>Revenue by Staff Member</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Revenue (AED)</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="B85C1E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="B85C1E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Staff &amp; Operations'!$B$5:$B$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Staff &amp; Operations'!$F$4:$F$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="80"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -1118,7 +1833,198 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>66</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>53</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="3600000"/>
@@ -1140,10 +2046,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>29</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6480000" cy="3600000"/>
+    <ext cx="5760000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1153,82 +2059,6 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>12</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5040000" cy="3600000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>27</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6480000" cy="3600000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>13</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6480000" cy="3600000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1526,192 +2356,326 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F14"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1"/>
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Al Matar Restaurant — Monthly Business Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="8" customHeight="1">
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>January 2026 | Sharjah, UAE</t>
+          <t>Al Matar Restaurant — Executive Dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Total Expenses</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Net Profit</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Profit Margin</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Total Orders</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Avg Order Value</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>AED 187,450</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>AED 142,800</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>AED 44,650</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>23.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Total Expenses</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Net Profit</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="C5" s="3" t="n">
+        <v>1847500</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1218350</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>629150</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>34280</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>53.88</v>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7" ht="28" customHeight="1">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Revenue (AED)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Expenses (AED)</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Net Profit (AED)</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Profit Margin</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="12" customHeight="1"/>
-    <row r="8" ht="28" customHeight="1">
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Revenue (AED)</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Expenses (AED)</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Net Profit (AED)</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Profit Margin</t>
-        </is>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Orders</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Avg Order (AED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Aug 2025</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>278500</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>189200</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>89300</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>5120</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>54.39</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Sep 2025</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>296800</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>198500</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>98300</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>5480</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>54.16</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n">
-        <v>165200</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>138500</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>26700</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>0.162</v>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="9" t="inlineStr">
+      <c r="C10" s="8" t="n">
+        <v>312400</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>205600</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>106800</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>5790</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>53.95</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Nov 2025</t>
         </is>
       </c>
-      <c r="C10" s="10" t="n">
-        <v>172800</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>140200</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>32600</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>0.189</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="6" t="inlineStr">
+      <c r="C11" s="12" t="n">
+        <v>325600</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>213400</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>112200</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>5960</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>54.63</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n">
-        <v>198500</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>151300</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>47200</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>0.238</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="9" t="inlineStr">
+      <c r="C12" s="8" t="n">
+        <v>308900</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>202650</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>106250</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>5720</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="C12" s="10" t="n">
-        <v>187450</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>142800</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>44650</v>
-      </c>
-      <c r="F12" s="11" t="n">
-        <v>0.238</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="4" t="inlineStr">
+      <c r="C13" s="12" t="n">
+        <v>325300</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>209000</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>116300</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>6210</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>52.38</v>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>1847500</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>1218350</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>629150</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <v>34280</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>53.88</v>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32" ht="20" customHeight="1">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>Prepared by Ahmed Ali | Data Analysis Services | ahmed-ali-ops.vercel.app</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B14:F14"/>
+  <mergeCells count="2">
+    <mergeCell ref="B32:M32"/>
+    <mergeCell ref="B2:M2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1724,197 +2688,919 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F13"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1"/>
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Sales by Category — January 2026</t>
+          <t>Sales Performance — January 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="28" customHeight="1">
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Revenue (AED)</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>% of Revenue</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Avg Order (AED)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>% of Revenue</t>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>YoY Growth</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Trend</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Grills &amp; BBQ</t>
         </is>
       </c>
-      <c r="C5" s="7" t="n">
-        <v>1240</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>52080</v>
-      </c>
-      <c r="E5" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>0.278</v>
+      <c r="C5" s="8" t="n">
+        <v>1420</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>128500</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>90.48999999999999</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>▲ Up</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Rice &amp; Biryani</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n">
-        <v>980</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>33320</v>
+      <c r="C6" s="12" t="n">
+        <v>1380</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>95600</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>34</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>0.178</v>
+        <v>0.2938</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>69.28</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>▲ Up</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Shawarma</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n">
-        <v>1560</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>37440</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>0.2</v>
+      <c r="C7" s="8" t="n">
+        <v>1650</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>72600</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>0.2232</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>▲ Up</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Beverages</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n">
-        <v>2100</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>25200</v>
+      <c r="C8" s="12" t="n">
+        <v>5800</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>40600</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>0.134</v>
+        <v>0.1248</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>→ Stable</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Desserts</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n">
-        <v>640</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>17280</v>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>0.092</v>
+      <c r="C9" s="8" t="n">
+        <v>920</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>28400</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>0.0873</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>30.87</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>▼ Down</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Appetizers</t>
         </is>
       </c>
-      <c r="C10" s="10" t="n">
-        <v>890</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>22130</v>
+      <c r="C10" s="12" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>24200</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>0.118</v>
-      </c>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="B11" s="14" t="inlineStr">
+        <v>0.07439999999999999</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>→ Stable</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Seafood</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>32500</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>0.0999</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>77.38</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>▲ Up</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Salads</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>680</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>18500</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>27.21</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>→ Stable</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C11" s="15" t="n">
-        <v>7410</v>
-      </c>
-      <c r="D11" s="15" t="n">
-        <v>187450</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="F11" s="17" t="n">
+      <c r="C13" s="16" t="n">
+        <v>13370</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>325300</v>
+      </c>
+      <c r="E13" s="17" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="4" t="inlineStr">
+      <c r="F13" s="18" t="n">
+        <v>36.23</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33" ht="28" customHeight="1">
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Revenue (AED)</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Orders</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Top Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>9800</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>188</v>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>Grills &amp; BBQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="B35" s="21" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="n">
+        <v>10200</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>196</v>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>Shawarma</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>11500</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>220</v>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>Rice &amp; Biryani</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="n">
+        <v>10800</v>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>208</v>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>Grills &amp; BBQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>11200</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>215</v>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>Seafood</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="B39" s="21" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="n">
+        <v>10600</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>204</v>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>Shawarma</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>10100</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>194</v>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>Rice &amp; Biryani</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="B41" s="21" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="n">
+        <v>9900</v>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>190</v>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>Grills &amp; BBQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="n">
+        <v>10400</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="B43" s="21" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="n">
+        <v>11000</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>212</v>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>Shawarma</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="B44" s="20" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>10800</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>208</v>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Grills &amp; BBQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="B45" s="21" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="n">
+        <v>11200</v>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>215</v>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>Rice &amp; Biryani</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="n">
+        <v>10600</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>204</v>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>Shawarma</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="B47" s="21" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="n">
+        <v>11500</v>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>221</v>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>Seafood</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="n">
+        <v>10900</v>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>210</v>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>Grills &amp; BBQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="B49" s="21" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="n">
+        <v>11100</v>
+      </c>
+      <c r="D49" s="12" t="n">
+        <v>214</v>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>Rice &amp; Biryani</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="B50" s="20" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="n">
+        <v>10400</v>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>Shawarma</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="B51" s="21" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="n">
+        <v>9800</v>
+      </c>
+      <c r="D51" s="12" t="n">
+        <v>188</v>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>Grills &amp; BBQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="B52" s="22" t="inlineStr">
         <is>
           <t>Prepared by Ahmed Ali | Data Analysis Services | ahmed-ali-ops.vercel.app</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="B53" s="21" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="n">
+        <v>10300</v>
+      </c>
+      <c r="D53" s="12" t="n">
+        <v>198</v>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>Rice &amp; Biryani</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="B54" s="20" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="n">
+        <v>11200</v>
+      </c>
+      <c r="D54" s="8" t="n">
+        <v>215</v>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>Grills &amp; BBQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="B55" s="21" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="n">
+        <v>10900</v>
+      </c>
+      <c r="D55" s="12" t="n">
+        <v>210</v>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>Shawarma</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="B56" s="20" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="n">
+        <v>11600</v>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>223</v>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>Seafood</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="B57" s="21" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="n">
+        <v>10100</v>
+      </c>
+      <c r="D57" s="12" t="n">
+        <v>194</v>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>Grills &amp; BBQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="B58" s="20" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="n">
+        <v>10800</v>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>208</v>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>Rice &amp; Biryani</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="B59" s="21" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="n">
+        <v>11300</v>
+      </c>
+      <c r="D59" s="12" t="n">
+        <v>218</v>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>Shawarma</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="n">
+        <v>10500</v>
+      </c>
+      <c r="D60" s="8" t="n">
+        <v>202</v>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Grills &amp; BBQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="B61" s="21" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="n">
+        <v>10200</v>
+      </c>
+      <c r="D61" s="12" t="n">
+        <v>196</v>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="B62" s="20" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="n">
+        <v>11000</v>
+      </c>
+      <c r="D62" s="8" t="n">
+        <v>212</v>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Grills &amp; BBQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="B63" s="21" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="n">
+        <v>11400</v>
+      </c>
+      <c r="D63" s="12" t="n">
+        <v>219</v>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>Rice &amp; Biryani</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="B64" s="20" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="n">
+        <v>10900</v>
+      </c>
+      <c r="D64" s="8" t="n">
+        <v>210</v>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>Shawarma</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="26" customHeight="1">
+      <c r="B65" s="23" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="n">
+        <v>332700</v>
+      </c>
+      <c r="D65" s="16" t="n">
+        <v>6398</v>
+      </c>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B52:I52"/>
+    <mergeCell ref="B2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1927,15 +3613,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F15"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1"/>
@@ -1948,223 +3637,747 @@
     </row>
     <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="28" customHeight="1">
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Budget (AED)</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Actual (AED)</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Variance (AED)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Variance %</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Rent</t>
         </is>
       </c>
-      <c r="C5" s="7" t="n">
-        <v>35000</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>35000</v>
-      </c>
-      <c r="E5" s="7" t="n">
+      <c r="C5" s="8" t="n">
+        <v>45000</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E5" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="18" t="inlineStr">
-        <is>
-          <t>On Track</t>
+      <c r="F5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>On Budget</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Fixed lease</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Staff Salaries</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="12" t="n">
+        <v>68000</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>69500</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>-1500</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>-0.0221</v>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>Over Budget</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>Overtime pay</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Food Supplies</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
         <v>42000</v>
       </c>
-      <c r="D6" s="10" t="n">
-        <v>43500</v>
-      </c>
-      <c r="E6" s="19" t="n">
+      <c r="D7" s="8" t="n">
+        <v>39800</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>0.0524</v>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Under Budget</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Bulk discount</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>13200</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>-1200</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>Over Budget</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>AC usage high</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>14800</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>On Budget</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Social media ads</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>9200</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>-1200</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>Over Budget</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>Kitchen repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Delivery Commissions</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>11500</v>
+      </c>
+      <c r="E11" s="8" t="n">
         <v>-1500</v>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F11" s="9" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>Over Budget</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="6" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Talabat surge</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>On Budget</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Annual policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>POS Fees</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>3100</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>-100</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>-0.0333</v>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>On Budget</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Card transactions</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Cleaning</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>3800</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>Under Budget</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>Negotiated rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Miscellaneous</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>5400</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Under Budget</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Lower than expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Licenses</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>On Budget</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>Annual renewal</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="n">
+        <v>220000</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>222300</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>0.01045454545454545</v>
+      </c>
+      <c r="G17" s="15" t="inlineStr"/>
+      <c r="H17" s="15" t="inlineStr"/>
+    </row>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37" ht="28" customHeight="1">
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Nov 2025</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>45000</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>45000</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Staff Salaries</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="n">
+        <v>67200</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>68000</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>68500</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>69500</v>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Food Supplies</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n">
-        <v>28000</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>26800</v>
-      </c>
-      <c r="E7" s="21" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F7" s="22" t="inlineStr">
-        <is>
-          <t>Under Budget</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="9" t="inlineStr">
+      <c r="C40" s="8" t="n">
+        <v>41500</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>40200</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>40800</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>39800</v>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n">
-        <v>8000</v>
-      </c>
-      <c r="D8" s="10" t="n">
+      <c r="C41" s="12" t="n">
+        <v>11500</v>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>11800</v>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>12400</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>13200</v>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="n">
+        <v>14000</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>14500</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>15200</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="n">
+        <v>7500</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>8200</v>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>7800</v>
+      </c>
+      <c r="F43" s="12" t="n">
         <v>9200</v>
       </c>
-      <c r="E8" s="19" t="n">
-        <v>-1200</v>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>Over Budget</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n">
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Delivery Commissions</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>9500</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>10200</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>10800</v>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>11500</v>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="D9" s="7" t="n">
-        <v>4800</v>
-      </c>
-      <c r="E9" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
-        <is>
-          <t>Under Budget</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>3500</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>3200</v>
-      </c>
-      <c r="E10" s="21" t="n">
-        <v>300</v>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>Under Budget</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Delivery Commissions</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>13100</v>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>-1100</v>
-      </c>
-      <c r="F11" s="24" t="inlineStr">
-        <is>
-          <t>Over Budget</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="9" t="inlineStr">
+      <c r="D45" s="12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>POS Fees</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="n">
+        <v>2800</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>2900</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>2950</v>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>Cleaning</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="n">
+        <v>4200</v>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>3900</v>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>Miscellaneous</t>
         </is>
       </c>
-      <c r="C12" s="10" t="n">
-        <v>6000</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>7200</v>
-      </c>
-      <c r="E12" s="19" t="n">
-        <v>-1200</v>
-      </c>
-      <c r="F12" s="20" t="inlineStr">
-        <is>
-          <t>Over Budget</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="B13" s="14" t="inlineStr">
+      <c r="C48" s="8" t="n">
+        <v>5800</v>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>5700</v>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>Licenses</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D49" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E49" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F49" s="12" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="50" ht="26" customHeight="1">
+      <c r="B50" s="24" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C13" s="15" t="n">
-        <v>139500</v>
-      </c>
-      <c r="D13" s="15" t="n">
-        <v>142800</v>
-      </c>
-      <c r="E13" s="25" t="n">
-        <v>-3300</v>
-      </c>
-      <c r="F13" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="C50" s="25" t="n">
+        <v>216000</v>
+      </c>
+      <c r="D50" s="25" t="n">
+        <v>217300</v>
+      </c>
+      <c r="E50" s="25" t="n">
+        <v>220050</v>
+      </c>
+      <c r="F50" s="25" t="n">
+        <v>222300</v>
+      </c>
+    </row>
+    <row r="51"/>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Nov 2025</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="26" t="n">
+        <v>216000</v>
+      </c>
+      <c r="C53" s="26" t="n">
+        <v>217300</v>
+      </c>
+      <c r="D53" s="26" t="n">
+        <v>220050</v>
+      </c>
+      <c r="E53" s="26" t="n">
+        <v>222300</v>
+      </c>
+    </row>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58" ht="20" customHeight="1">
+      <c r="B58" s="19" t="inlineStr">
         <is>
           <t>Prepared by Ahmed Ali | Data Analysis Services | ahmed-ali-ops.vercel.app</t>
         </is>
@@ -2172,9 +4385,25 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B58:I58"/>
+    <mergeCell ref="B2:I2"/>
   </mergeCells>
+  <conditionalFormatting sqref="F5:F16">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5:G16">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
+      <formula>"Over Budget"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="1">
+      <formula>"Under Budget"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -2186,118 +4415,434 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:D12"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1"/>
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Key Insights &amp; Recommendations</t>
+          <t>Staff Performance &amp; Operations — January 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="28" customHeight="1">
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="B5" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Profit margin improved from 16.2% to 23.8% over 4 months — strong upward trend</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="B6" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Shawarma has the highest order volume (1,560) but below-average ticket size (AED 24). Consider combo upselling.</t>
-        </is>
-      </c>
-      <c r="D6" s="29" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="B7" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Staff salaries exceeded budget by AED 1,500. Review overtime hours.</t>
-        </is>
-      </c>
-      <c r="D7" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="B8" s="28" t="n">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Hours Worked</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Clients Served</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Revenue Generated (AED)</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Efficiency Score</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Mohammed Al Suwaidi</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Head Chef</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>220</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>890</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>142500</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H5" s="28" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Fatima Al Zaabi</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Floor Manager</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>98000</v>
+      </c>
+      <c r="G6" s="29" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H6" s="30" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Ahmed Hassan</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Grill Master</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>210</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>720</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>86500</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H7" s="28" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Sara Ibrahim</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>190</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>52300</v>
+      </c>
+      <c r="G8" s="29" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H8" s="30" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Khalid Omar</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Waiter</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>180</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>48200</v>
+      </c>
+      <c r="G9" s="27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H9" s="28" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Nour Ali</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Pastry Chef</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>580</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>38900</v>
+      </c>
+      <c r="G10" s="29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H10" s="30" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Youssef Majeed</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Delivery Lead</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>195</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>980</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>42100</v>
+      </c>
+      <c r="G11" s="27" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H11" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Delivery commissions are 9.2% over budget. Negotiate better rates with Talabat/Noon Food.</t>
-        </is>
-      </c>
-      <c r="D8" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="B9" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>December peak revenue (AED 198,500) was seasonal. Plan promotions for slower months.</t>
-        </is>
-      </c>
-      <c r="D9" s="30" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="4" t="inlineStr">
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Mariam Saeed</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Hostess</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>175</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>35400</v>
+      </c>
+      <c r="G12" s="29" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H12" s="30" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr"/>
+      <c r="D13" s="16" t="n">
+        <v>1570</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>10220</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>543900</v>
+      </c>
+      <c r="G13" s="31" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H13" s="32" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33" ht="28" customHeight="1">
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Time Slot</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Avg Orders</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Avg Revenue (AED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>10:00 AM – 12:00 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>12:00 PM – 2:00 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="n">
+        <v>128</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>6920</v>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>2:00 PM – 5:00 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>3350</v>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>5:00 PM – 8:00 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>7830</v>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>8:00 PM – 10:00 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>5290</v>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>10:00 PM – 12:00 AM</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>2270</v>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53" ht="20" customHeight="1">
+      <c r="B53" s="19" t="inlineStr">
         <is>
           <t>Prepared by Ahmed Ali | Data Analysis Services | ahmed-ali-ops.vercel.app</t>
         </is>
@@ -2305,9 +4850,347 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B53:I53"/>
+    <mergeCell ref="B2:I2"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1"/>
+    <row r="2" ht="32" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Key Insights &amp; Strategic Recommendations</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Action Item</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Seafood category shows highest YoY growth (18%) with strong margins</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Expand seafood menu with 3-4 new premium items</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Evening peak (5-8 PM) generates 29% of daily revenue</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Add 2 staff members during evening shift</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Cost Control</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Delivery commissions exceed budget by 15% due to Talabat surge pricing</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Negotiate flat-rate commission or add direct ordering channel</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Beverage category has low avg order value (AED 7) but high volume</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>Introduce combo deals pairing beverages with main dishes</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Mohammed Al Suwaidi generates 26% of total revenue as Head Chef</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Develop succession plan and document signature recipes</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Dessert category declined 3% YoY despite overall growth</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>Introduce seasonal dessert specials and loyalty discounts</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Efficiency</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Kitchen maintenance costs spiked 15% due to aging equipment</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Schedule preventive maintenance and budget for equipment upgrade</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Profit margin improved to 35.7% in Jan — highest in 6 months</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Reinvest margin gains into marketing for customer acquisition</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15" ht="20" customHeight="1">
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>Prepared by Ahmed Ali | Data Analysis Services | ahmed-ali-ops.vercel.app</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B15:H15"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G5:G12">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"High"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="2">
+      <formula>"Medium"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
+      <formula>"Low"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E12">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
+      <formula>"High"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="2">
+      <formula>"Medium"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>